--- a/sheets/조재수대금교본/검수/죽성가.xlsx
+++ b/sheets/조재수대금교본/검수/죽성가.xlsx
@@ -3069,7 +3069,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3106,14 +3106,14 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌ʊ
+          <t xml:space="preserve">㴌
 –</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌ʊ
+          <t xml:space="preserve">㴌
 –</t>
         </is>
       </c>
@@ -3129,8 +3129,8 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳c
-湳c</t>
+          <t xml:space="preserve">湳
+湳</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -3147,17 +3147,9 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="24"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
@@ -3165,11 +3157,7 @@
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
@@ -3214,38 +3202,34 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-Z潢</t>
+潢</t>
         </is>
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-Z潢</t>
+潢</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B7" s="21"/>
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
@@ -3257,8 +3241,8 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
-汰c</t>
+          <t xml:space="preserve">汰
+汰</t>
         </is>
       </c>
       <c r="I7" s="23"/>
@@ -3284,54 +3268,31 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-⊏∼
-‹</t>
+∼</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∼
-‹</t>
+          <t xml:space="preserve">㴌∼</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∼
-‹</t>
+          <t xml:space="preserve">㴌∼</t>
         </is>
       </c>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="138.71" customHeight="true">
@@ -3345,7 +3306,6 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-⊏
 –</t>
         </is>
       </c>
@@ -3386,7 +3346,6 @@
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-⊏
 –</t>
         </is>
       </c>
@@ -3394,24 +3353,16 @@
     </row>
     <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="23"/>
       <c r="D10" s="21"/>
       <c r="E10" s="23"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢c
-潢c</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -3419,8 +3370,8 @@
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌c
-㴌c</t>
+          <t xml:space="preserve">㴌
+㴌</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -3438,63 +3389,45 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-⊏∼
-‹</t>
+∼</t>
         </is>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼
-⊏
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼
-⊏
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-⊏∼
-‹</t>
+∼</t>
         </is>
       </c>
       <c r="I11" s="24"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="J11" s="21"/>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-⊏∼
-‹</t>
+∼</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-ﾉ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O11" s="24"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ</t>
-        </is>
-      </c>
+      <c r="P11" s="21"/>
       <c r="Q11" s="24"/>
     </row>
     <row r="12" ht="138.71" customHeight="true">
@@ -3544,7 +3477,7 @@
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-Z林</t>
+林</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -3581,23 +3514,11 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21"/>
       <c r="K14" s="24"/>

--- a/sheets/조재수대금교본/검수/죽성가.xlsx
+++ b/sheets/조재수대금교본/검수/죽성가.xlsx
@@ -3069,7 +3069,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3106,14 +3106,14 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
+          <t xml:space="preserve">㴌ʊ
 –</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
+          <t xml:space="preserve">㴌ʊ
 –</t>
         </is>
       </c>
@@ -3129,8 +3129,8 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-湳</t>
+          <t xml:space="preserve">湳c
+湳c</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -3202,27 +3202,27 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+Z潢</t>
         </is>
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+Z潢</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -3241,8 +3241,8 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">汰c
+汰c</t>
         </is>
       </c>
       <c r="I7" s="23"/>
@@ -3268,7 +3268,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-∼</t>
+⊏∼</t>
         </is>
       </c>
       <c r="C8" s="24"/>
@@ -3306,6 +3306,7 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
+⊏
 –</t>
         </is>
       </c>
@@ -3346,6 +3347,7 @@
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
+⊏
 –</t>
         </is>
       </c>
@@ -3361,8 +3363,8 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢</t>
+          <t xml:space="preserve">潢c
+潢c</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -3370,8 +3372,8 @@
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-㴌</t>
+          <t xml:space="preserve">㴌c
+㴌c</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -3389,45 +3391,57 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-∼</t>
+⊏∼</t>
         </is>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢∼
+⊏</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢∼
+⊏</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-∼</t>
+⊏∼</t>
         </is>
       </c>
       <c r="I11" s="24"/>
-      <c r="J11" s="21"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-∼</t>
+⊏∼</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+ﾉ</t>
         </is>
       </c>
       <c r="O11" s="24"/>
-      <c r="P11" s="21"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="Q11" s="24"/>
     </row>
     <row r="12" ht="138.71" customHeight="true">
@@ -3477,7 +3491,7 @@
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林</t>
+Z林</t>
         </is>
       </c>
       <c r="Q12" s="22"/>

--- a/sheets/조재수대금교본/검수/죽성가.xlsx
+++ b/sheets/조재수대금교본/검수/죽성가.xlsx
@@ -3021,28 +3021,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="16.2" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.2" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="16.2" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="93.02" customHeight="true">
+    <row r="2" ht="85.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="138.71" customHeight="true">
+    <row r="3" ht="126.87" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="138.71" customHeight="true">
+    <row r="4" ht="126.87" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3143,7 +3143,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="138.71" customHeight="true">
+    <row r="5" ht="126.87" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -3171,7 +3171,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="138.71" customHeight="true">
+    <row r="6" ht="126.87" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="138.71" customHeight="true">
+    <row r="7" ht="126.87" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="138.71" customHeight="true">
+    <row r="8" ht="126.87" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="138.71" customHeight="true">
+    <row r="9" ht="126.87" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="138.71" customHeight="true">
+    <row r="10" ht="126.87" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3386,7 +3386,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="138.71" customHeight="true">
+    <row r="11" ht="126.87" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="138.71" customHeight="true">
+    <row r="12" ht="126.87" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="138.71" customHeight="true">
+    <row r="13" ht="126.87" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="138.71" customHeight="true">
+    <row r="14" ht="126.87" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3549,6 +3549,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="47"/>
 </worksheet>
 </file>